--- a/extenbooks/XS007_extenbook.xlsx
+++ b/extenbooks/XS007_extenbook.xlsx
@@ -711,7 +711,7 @@
         <v>97.523</v>
       </c>
       <c r="C5" t="n">
-        <v>102.4946531791908</v>
+        <v>102.4946531791907</v>
       </c>
       <c r="D5" t="n">
         <v>72.30000000000001</v>
@@ -946,7 +946,7 @@
         <v>1943</v>
       </c>
       <c r="B22" t="n">
-        <v>97.72799999999999</v>
+        <v>97.72800000000001</v>
       </c>
       <c r="C22" t="n">
         <v>102.7101039333896</v>
@@ -963,7 +963,7 @@
         <v>95.128</v>
       </c>
       <c r="C23" t="n">
-        <v>99.97755778257496</v>
+        <v>99.97755778257495</v>
       </c>
       <c r="D23" t="n">
         <v>70.52443423602637</v>
@@ -1120,7 +1120,7 @@
         <v>231.6307461995541</v>
       </c>
       <c r="D34" t="n">
-        <v>190.0765450201492</v>
+        <v>190.0765450201491</v>
       </c>
     </row>
     <row r="35">
@@ -1148,7 +1148,7 @@
         <v>282.1494145935728</v>
       </c>
       <c r="D36" t="n">
-        <v>232.0765450201492</v>
+        <v>232.0765450201491</v>
       </c>
     </row>
     <row r="37">
@@ -1162,7 +1162,7 @@
         <v>289.6913884688392</v>
       </c>
       <c r="D37" t="n">
-        <v>248.0765450201492</v>
+        <v>248.0765450201491</v>
       </c>
     </row>
     <row r="38">
@@ -1246,7 +1246,7 @@
         <v>369.7811391065325</v>
       </c>
       <c r="D43" t="n">
-        <v>367.1765450201492</v>
+        <v>367.1765450201491</v>
       </c>
     </row>
     <row r="44">
@@ -1495,7 +1495,7 @@
         <v/>
       </c>
       <c r="C61" t="n">
-        <v>2790.590639341792</v>
+        <v>2790.590639341791</v>
       </c>
       <c r="D61" t="n">
         <v>2093.776545020149</v>
@@ -1579,7 +1579,7 @@
         <v/>
       </c>
       <c r="C67" t="n">
-        <v>3794.134502412666</v>
+        <v>3794.134502412667</v>
       </c>
       <c r="D67" t="n">
         <v>3361.076545020149</v>
@@ -1845,7 +1845,7 @@
         <v/>
       </c>
       <c r="C86" t="n">
-        <v>11016.56182755366</v>
+        <v>11016.56182755367</v>
       </c>
       <c r="D86" t="n">
         <v>9706.876545020148</v>
@@ -1859,7 +1859,7 @@
         <v/>
       </c>
       <c r="C87" t="n">
-        <v>11695.53919696292</v>
+        <v>11695.53919696291</v>
       </c>
       <c r="D87" t="n">
         <v>10229.67654502015</v>
@@ -1969,14 +1969,14 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>1925</v>
+        <v>1926</v>
       </c>
       <c r="B97" t="n">
-        <v>98.09999999999999</v>
+        <v>97.523</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>XS007-B</t>
+          <t>XS007-A</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -1992,14 +1992,14 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>1925</v>
+        <v>1927</v>
       </c>
       <c r="B98" t="n">
-        <v>69.2</v>
+        <v>104.945</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>XS007-C</t>
+          <t>XS007-A</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -2015,10 +2015,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>1926</v>
+        <v>1928</v>
       </c>
       <c r="B99" t="n">
-        <v>97.523</v>
+        <v>109.931</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -2038,14 +2038,14 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>1926</v>
+        <v>1929</v>
       </c>
       <c r="B100" t="n">
-        <v>102.4946531791908</v>
+        <v>116.446</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>XS007-B</t>
+          <t>XS007-A</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -2061,14 +2061,14 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>1926</v>
+        <v>1930</v>
       </c>
       <c r="B101" t="n">
-        <v>72.30000000000001</v>
+        <v>120.994</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>XS007-C</t>
+          <t>XS007-A</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -2084,10 +2084,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>1927</v>
+        <v>1931</v>
       </c>
       <c r="B102" t="n">
-        <v>104.945</v>
+        <v>114.303</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -2107,14 +2107,14 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>1927</v>
+        <v>1932</v>
       </c>
       <c r="B103" t="n">
-        <v>110.2950214604778</v>
+        <v>108.553</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>XS007-B</t>
+          <t>XS007-A</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -2130,14 +2130,14 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>1927</v>
+        <v>1933</v>
       </c>
       <c r="B104" t="n">
-        <v>77.80240045937882</v>
+        <v>104.958</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>XS007-C</t>
+          <t>XS007-A</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -2153,10 +2153,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>1928</v>
+        <v>1934</v>
       </c>
       <c r="B105" t="n">
-        <v>109.931</v>
+        <v>102.751</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -2176,14 +2176,14 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>1928</v>
+        <v>1935</v>
       </c>
       <c r="B106" t="n">
-        <v>115.5352041943092</v>
+        <v>100.48</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>XS007-B</t>
+          <t>XS007-A</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -2199,14 +2199,14 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>1928</v>
+        <v>1936</v>
       </c>
       <c r="B107" t="n">
-        <v>81.49883924817735</v>
+        <v>97.873</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>XS007-C</t>
+          <t>XS007-A</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -2222,10 +2222,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>1929</v>
+        <v>1937</v>
       </c>
       <c r="B108" t="n">
-        <v>116.446</v>
+        <v>100.32</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -2245,14 +2245,14 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>1929</v>
+        <v>1938</v>
       </c>
       <c r="B109" t="n">
-        <v>122.3823342606774</v>
+        <v>99.29900000000001</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>XS007-B</t>
+          <t>XS007-A</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -2268,14 +2268,14 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>1929</v>
+        <v>1939</v>
       </c>
       <c r="B110" t="n">
-        <v>86.32882294433108</v>
+        <v>100.226</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>XS007-C</t>
+          <t>XS007-A</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -2291,10 +2291,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>1930</v>
+        <v>1940</v>
       </c>
       <c r="B111" t="n">
-        <v>120.994</v>
+        <v>100.214</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -2314,14 +2314,14 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>1930</v>
+        <v>1941</v>
       </c>
       <c r="B112" t="n">
-        <v>127.1621880660255</v>
+        <v>100.698</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>XS007-B</t>
+          <t>XS007-A</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -2337,14 +2337,14 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>1930</v>
+        <v>1942</v>
       </c>
       <c r="B113" t="n">
-        <v>89.70054448694155</v>
+        <v>99.77200000000001</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>XS007-C</t>
+          <t>XS007-A</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -2360,10 +2360,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>1931</v>
+        <v>1943</v>
       </c>
       <c r="B114" t="n">
-        <v>114.303</v>
+        <v>97.72800000000001</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -2383,14 +2383,14 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>1931</v>
+        <v>1944</v>
       </c>
       <c r="B115" t="n">
-        <v>120.1300856448329</v>
+        <v>95.128</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>XS007-B</t>
+          <t>XS007-A</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -2406,14 +2406,14 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>1931</v>
+        <v>1945</v>
       </c>
       <c r="B116" t="n">
-        <v>84.74008080145197</v>
+        <v>92.057</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>XS007-C</t>
+          <t>XS007-A</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -2429,10 +2429,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>1932</v>
+        <v>1946</v>
       </c>
       <c r="B117" t="n">
-        <v>108.553</v>
+        <v>100.329</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -2452,14 +2452,14 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>1932</v>
+        <v>1947</v>
       </c>
       <c r="B118" t="n">
-        <v>114.0869547343775</v>
+        <v>112.194</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>XS007-B</t>
+          <t>XS007-A</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -2475,14 +2475,14 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>1932</v>
+        <v>1948</v>
       </c>
       <c r="B119" t="n">
-        <v>80.47724024076372</v>
+        <v>125.65</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>XS007-C</t>
+          <t>XS007-A</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -2498,10 +2498,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>1933</v>
+        <v>1949</v>
       </c>
       <c r="B120" t="n">
-        <v>104.958</v>
+        <v>135.617</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -2521,14 +2521,14 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>1933</v>
+        <v>1950</v>
       </c>
       <c r="B121" t="n">
-        <v>110.3086841912318</v>
+        <v>144.691</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>XS007-B</t>
+          <t>XS007-A</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -2544,14 +2544,14 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>1933</v>
+        <v>1951</v>
       </c>
       <c r="B122" t="n">
-        <v>77.81203818586386</v>
+        <v>159.325</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>XS007-C</t>
+          <t>XS007-A</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -2567,10 +2567,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>1934</v>
+        <v>1952</v>
       </c>
       <c r="B123" t="n">
-        <v>102.751</v>
+        <v>169.546</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -2590,14 +2590,14 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>1934</v>
+        <v>1953</v>
       </c>
       <c r="B124" t="n">
-        <v>107.9891729009057</v>
+        <v>180.612</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>XS007-B</t>
+          <t>XS007-A</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -2613,14 +2613,14 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>1934</v>
+        <v>1954</v>
       </c>
       <c r="B125" t="n">
-        <v>76.17584877413533</v>
+        <v>191.437</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>XS007-C</t>
+          <t>XS007-A</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -2636,10 +2636,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>1935</v>
+        <v>1955</v>
       </c>
       <c r="B126" t="n">
-        <v>100.48</v>
+        <v>206.388</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -2659,14 +2659,14 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>1935</v>
+        <v>1956</v>
       </c>
       <c r="B127" t="n">
-        <v>105.602398936098</v>
+        <v>225.862</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>XS007-B</t>
+          <t>XS007-A</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -2682,14 +2682,14 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>1935</v>
+        <v>1957</v>
       </c>
       <c r="B128" t="n">
-        <v>74.49221209355741</v>
+        <v>244.463</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>XS007-C</t>
+          <t>XS007-A</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -2705,10 +2705,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>1936</v>
+        <v>1958</v>
       </c>
       <c r="B129" t="n">
-        <v>97.873</v>
+        <v>259.613</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -2728,14 +2728,14 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>1936</v>
+        <v>1959</v>
       </c>
       <c r="B130" t="n">
-        <v>102.8624959302619</v>
+        <v>275.772</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>XS007-B</t>
+          <t>XS007-A</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -2751,14 +2751,14 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>1936</v>
+        <v>1960</v>
       </c>
       <c r="B131" t="n">
-        <v>72.55947725152015</v>
+        <v>293.215</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>XS007-C</t>
+          <t>XS007-A</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -2774,10 +2774,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>1937</v>
+        <v>1961</v>
       </c>
       <c r="B132" t="n">
-        <v>100.32</v>
+        <v>310.266</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -2797,14 +2797,14 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>1937</v>
+        <v>1962</v>
       </c>
       <c r="B133" t="n">
-        <v>105.434242249894</v>
+        <v>333.9924528133036</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>XS007-B</t>
+          <t>XS007-A</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -2820,14 +2820,14 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>1937</v>
+        <v>1963</v>
       </c>
       <c r="B134" t="n">
-        <v>74.37359392143392</v>
+        <v>342.026</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>XS007-C</t>
+          <t>XS007-A</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -2843,10 +2843,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>1938</v>
+        <v>1964</v>
       </c>
       <c r="B135" t="n">
-        <v>99.29900000000001</v>
+        <v>365.551</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -2866,14 +2866,14 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>1938</v>
+        <v>1965</v>
       </c>
       <c r="B136" t="n">
-        <v>104.3611923960549</v>
+        <v>395.297</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>XS007-B</t>
+          <t>XS007-A</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -2889,14 +2889,14 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>1938</v>
+        <v>1966</v>
       </c>
       <c r="B137" t="n">
-        <v>73.61666171057084</v>
+        <v>432.034</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>XS007-C</t>
+          <t>XS007-A</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -2912,10 +2912,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>1939</v>
+        <v>1967</v>
       </c>
       <c r="B138" t="n">
-        <v>100.226</v>
+        <v>467.446</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -2935,14 +2935,14 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>1939</v>
+        <v>1968</v>
       </c>
       <c r="B139" t="n">
-        <v>105.3354501967492</v>
+        <v>504.865</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>XS007-B</t>
+          <t>XS007-A</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -2958,14 +2958,14 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>1939</v>
+        <v>1969</v>
       </c>
       <c r="B140" t="n">
-        <v>74.30390574531137</v>
+        <v>561.306</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>XS007-C</t>
+          <t>XS007-A</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -2981,10 +2981,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>1940</v>
+        <v>1970</v>
       </c>
       <c r="B141" t="n">
-        <v>100.214</v>
+        <v>599.465</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -3004,10 +3004,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>1940</v>
+        <v>1925</v>
       </c>
       <c r="B142" t="n">
-        <v>105.3228384452839</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -3027,14 +3027,14 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>1940</v>
+        <v>1926</v>
       </c>
       <c r="B143" t="n">
-        <v>74.2950093824021</v>
+        <v>102.4946531791907</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>XS007-C</t>
+          <t>XS007-B</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -3050,14 +3050,14 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>1941</v>
+        <v>1927</v>
       </c>
       <c r="B144" t="n">
-        <v>100.698</v>
+        <v>110.2950214604778</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>XS007-A</t>
+          <t>XS007-B</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -3073,10 +3073,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>1941</v>
+        <v>1928</v>
       </c>
       <c r="B145" t="n">
-        <v>105.8315124210509</v>
+        <v>115.5352041943092</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -3096,14 +3096,14 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>1941</v>
+        <v>1929</v>
       </c>
       <c r="B146" t="n">
-        <v>74.65382935307568</v>
+        <v>122.3823342606774</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>XS007-C</t>
+          <t>XS007-B</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -3119,14 +3119,14 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>1942</v>
+        <v>1930</v>
       </c>
       <c r="B147" t="n">
-        <v>99.77200000000001</v>
+        <v>127.1621880660255</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>XS007-A</t>
+          <t>XS007-B</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -3142,10 +3142,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>1942</v>
+        <v>1931</v>
       </c>
       <c r="B148" t="n">
-        <v>104.8583055996454</v>
+        <v>120.1300856448329</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -3165,14 +3165,14 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>1942</v>
+        <v>1932</v>
       </c>
       <c r="B149" t="n">
-        <v>73.96732668191093</v>
+        <v>114.0869547343775</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>XS007-C</t>
+          <t>XS007-B</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -3188,14 +3188,14 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>1943</v>
+        <v>1933</v>
       </c>
       <c r="B150" t="n">
-        <v>97.72799999999999</v>
+        <v>110.3086841912318</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>XS007-A</t>
+          <t>XS007-B</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -3211,10 +3211,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>1943</v>
+        <v>1934</v>
       </c>
       <c r="B151" t="n">
-        <v>102.7101039333896</v>
+        <v>107.9891729009057</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -3234,14 +3234,14 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>1943</v>
+        <v>1935</v>
       </c>
       <c r="B152" t="n">
-        <v>72.45197953303324</v>
+        <v>105.602398936098</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>XS007-C</t>
+          <t>XS007-B</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -3257,14 +3257,14 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>1944</v>
+        <v>1936</v>
       </c>
       <c r="B153" t="n">
-        <v>95.128</v>
+        <v>102.8624959302619</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>XS007-A</t>
+          <t>XS007-B</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -3280,10 +3280,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>1944</v>
+        <v>1937</v>
       </c>
       <c r="B154" t="n">
-        <v>99.97755778257496</v>
+        <v>105.434242249894</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -3303,14 +3303,14 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>1944</v>
+        <v>1938</v>
       </c>
       <c r="B155" t="n">
-        <v>70.52443423602637</v>
+        <v>104.3611923960549</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>XS007-C</t>
+          <t>XS007-B</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -3326,14 +3326,14 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>1945</v>
+        <v>1939</v>
       </c>
       <c r="B156" t="n">
-        <v>92.057</v>
+        <v>105.3354501967492</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>XS007-A</t>
+          <t>XS007-B</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -3349,10 +3349,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>1945</v>
+        <v>1940</v>
       </c>
       <c r="B157" t="n">
-        <v>96.75000038674736</v>
+        <v>105.3228384452839</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -3372,14 +3372,14 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>1945</v>
+        <v>1941</v>
       </c>
       <c r="B158" t="n">
-        <v>68.24770669483097</v>
+        <v>105.8315124210509</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>XS007-C</t>
+          <t>XS007-B</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -3395,14 +3395,14 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>1946</v>
+        <v>1942</v>
       </c>
       <c r="B159" t="n">
-        <v>100.329</v>
+        <v>104.8583055996454</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>XS007-A</t>
+          <t>XS007-B</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -3418,10 +3418,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>1946</v>
+        <v>1943</v>
       </c>
       <c r="B160" t="n">
-        <v>105.443701063493</v>
+        <v>102.7101039333896</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -3441,14 +3441,14 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>1946</v>
+        <v>1944</v>
       </c>
       <c r="B161" t="n">
-        <v>74.38026619361587</v>
+        <v>99.97755778257495</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>XS007-C</t>
+          <t>XS007-B</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -3464,14 +3464,14 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>1947</v>
+        <v>1945</v>
       </c>
       <c r="B162" t="n">
-        <v>112.194</v>
+        <v>96.75000038674736</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>XS007-A</t>
+          <t>XS007-B</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -3487,10 +3487,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>1947</v>
+        <v>1946</v>
       </c>
       <c r="B163" t="n">
-        <v>117.9135703248067</v>
+        <v>105.443701063493</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -3513,11 +3513,11 @@
         <v>1947</v>
       </c>
       <c r="B164" t="n">
-        <v>83.17654502014911</v>
+        <v>117.9135703248067</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>XS007-C</t>
+          <t>XS007-B</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -3536,11 +3536,11 @@
         <v>1948</v>
       </c>
       <c r="B165" t="n">
-        <v>125.65</v>
+        <v>132.6790727817832</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>XS007-A</t>
+          <t>XS007-B</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -3556,10 +3556,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>1948</v>
+        <v>1949</v>
       </c>
       <c r="B166" t="n">
-        <v>132.6790727817832</v>
+        <v>138.2407147408027</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -3579,14 +3579,14 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>1948</v>
+        <v>1950</v>
       </c>
       <c r="B167" t="n">
-        <v>95.77654502014911</v>
+        <v>157.6285252940197</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>XS007-C</t>
+          <t>XS007-B</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -3602,14 +3602,14 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>1949</v>
+        <v>1951</v>
       </c>
       <c r="B168" t="n">
-        <v>135.617</v>
+        <v>174.5250950810846</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>XS007-A</t>
+          <t>XS007-B</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -3625,10 +3625,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>1949</v>
+        <v>1952</v>
       </c>
       <c r="B169" t="n">
-        <v>138.2407147408027</v>
+        <v>187.6470054474738</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -3648,14 +3648,14 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>1949</v>
+        <v>1953</v>
       </c>
       <c r="B170" t="n">
-        <v>105.9765450201491</v>
+        <v>200.0481818077638</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>XS007-C</t>
+          <t>XS007-B</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -3671,14 +3671,14 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>1950</v>
+        <v>1954</v>
       </c>
       <c r="B171" t="n">
-        <v>144.691</v>
+        <v>208.4245358857812</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>XS007-A</t>
+          <t>XS007-B</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -3694,10 +3694,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>1950</v>
+        <v>1955</v>
       </c>
       <c r="B172" t="n">
-        <v>157.6285252940197</v>
+        <v>231.6307461995541</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -3717,14 +3717,14 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>1950</v>
+        <v>1956</v>
       </c>
       <c r="B173" t="n">
-        <v>116.8765450201491</v>
+        <v>260.0760630214572</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>XS007-C</t>
+          <t>XS007-B</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -3740,14 +3740,14 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>1951</v>
+        <v>1957</v>
       </c>
       <c r="B174" t="n">
-        <v>159.325</v>
+        <v>282.1494145935728</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>XS007-A</t>
+          <t>XS007-B</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -3763,10 +3763,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>1951</v>
+        <v>1958</v>
       </c>
       <c r="B175" t="n">
-        <v>174.5250950810846</v>
+        <v>289.6913884688392</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -3786,14 +3786,14 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>1951</v>
+        <v>1959</v>
       </c>
       <c r="B176" t="n">
-        <v>130.8765450201491</v>
+        <v>304.4298374935349</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>XS007-C</t>
+          <t>XS007-B</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -3809,14 +3809,14 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>1952</v>
+        <v>1960</v>
       </c>
       <c r="B177" t="n">
-        <v>169.546</v>
+        <v>312.6101402575088</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>XS007-A</t>
+          <t>XS007-B</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -3832,10 +3832,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>1952</v>
+        <v>1961</v>
       </c>
       <c r="B178" t="n">
-        <v>187.6470054474738</v>
+        <v>321.9175464872374</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -3855,14 +3855,14 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>1952</v>
+        <v>1962</v>
       </c>
       <c r="B179" t="n">
-        <v>145.0765450201491</v>
+        <v>334.3294258339792</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>XS007-C</t>
+          <t>XS007-B</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -3878,14 +3878,14 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>1953</v>
+        <v>1963</v>
       </c>
       <c r="B180" t="n">
-        <v>180.612</v>
+        <v>347.3337766832103</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>XS007-A</t>
+          <t>XS007-B</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -3901,10 +3901,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>1953</v>
+        <v>1964</v>
       </c>
       <c r="B181" t="n">
-        <v>200.0481818077638</v>
+        <v>369.7811391065325</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -3924,14 +3924,14 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>1953</v>
+        <v>1965</v>
       </c>
       <c r="B182" t="n">
-        <v>160.5765450201491</v>
+        <v>400.009371190676</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>XS007-C</t>
+          <t>XS007-B</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -3947,14 +3947,14 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>1954</v>
+        <v>1966</v>
       </c>
       <c r="B183" t="n">
-        <v>191.437</v>
+        <v>441.0617068986242</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>XS007-A</t>
+          <t>XS007-B</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -3970,10 +3970,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>1954</v>
+        <v>1967</v>
       </c>
       <c r="B184" t="n">
-        <v>208.4245358857812</v>
+        <v>482.69379367734</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -3993,14 +3993,14 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>1954</v>
+        <v>1968</v>
       </c>
       <c r="B185" t="n">
-        <v>174.5765450201491</v>
+        <v>535.7669998366205</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>XS007-C</t>
+          <t>XS007-B</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -4016,14 +4016,14 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>1955</v>
+        <v>1969</v>
       </c>
       <c r="B186" t="n">
-        <v>206.388</v>
+        <v>595.4111587393223</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>XS007-A</t>
+          <t>XS007-B</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -4039,10 +4039,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>1955</v>
+        <v>1970</v>
       </c>
       <c r="B187" t="n">
-        <v>231.6307461995541</v>
+        <v>660.0082194553752</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -4062,14 +4062,14 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>1955</v>
+        <v>1971</v>
       </c>
       <c r="B188" t="n">
-        <v>190.0765450201492</v>
+        <v>728.0561900232797</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>XS007-C</t>
+          <t>XS007-B</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -4085,14 +4085,14 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>1956</v>
+        <v>1972</v>
       </c>
       <c r="B189" t="n">
-        <v>225.862</v>
+        <v>795.5806463073883</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>XS007-A</t>
+          <t>XS007-B</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -4108,10 +4108,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>1956</v>
+        <v>1973</v>
       </c>
       <c r="B190" t="n">
-        <v>260.0760630214572</v>
+        <v>905.1470932422044</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -4131,14 +4131,14 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>1956</v>
+        <v>1974</v>
       </c>
       <c r="B191" t="n">
-        <v>210.1765450201491</v>
+        <v>1112.967142133053</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>XS007-C</t>
+          <t>XS007-B</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -4154,14 +4154,14 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>1957</v>
+        <v>1975</v>
       </c>
       <c r="B192" t="n">
-        <v>244.463</v>
+        <v>1239.942598214263</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>XS007-A</t>
+          <t>XS007-B</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -4177,10 +4177,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>1957</v>
+        <v>1976</v>
       </c>
       <c r="B193" t="n">
-        <v>282.1494145935728</v>
+        <v>1365.520802998242</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -4200,14 +4200,14 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>1957</v>
+        <v>1977</v>
       </c>
       <c r="B194" t="n">
-        <v>232.0765450201492</v>
+        <v>1524.571604949191</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>XS007-C</t>
+          <t>XS007-B</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -4223,14 +4223,14 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>1958</v>
+        <v>1978</v>
       </c>
       <c r="B195" t="n">
-        <v>259.613</v>
+        <v>1739.358507204221</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>XS007-A</t>
+          <t>XS007-B</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -4246,10 +4246,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>1958</v>
+        <v>1979</v>
       </c>
       <c r="B196" t="n">
-        <v>289.6913884688392</v>
+        <v>2010.474141529709</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -4269,14 +4269,14 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>1958</v>
+        <v>1980</v>
       </c>
       <c r="B197" t="n">
-        <v>248.0765450201492</v>
+        <v>2318.022960056148</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>XS007-C</t>
+          <t>XS007-B</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -4292,14 +4292,14 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>1959</v>
+        <v>1981</v>
       </c>
       <c r="B198" t="n">
-        <v>275.772</v>
+        <v>2626.419874620664</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>XS007-A</t>
+          <t>XS007-B</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -4315,10 +4315,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>1959</v>
+        <v>1982</v>
       </c>
       <c r="B199" t="n">
-        <v>304.4298374935349</v>
+        <v>2790.590639341791</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -4338,14 +4338,14 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>1959</v>
+        <v>1983</v>
       </c>
       <c r="B200" t="n">
-        <v>265.2765450201491</v>
+        <v>2873.790280472474</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>XS007-C</t>
+          <t>XS007-B</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -4361,14 +4361,14 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>1960</v>
+        <v>1984</v>
       </c>
       <c r="B201" t="n">
-        <v>293.215</v>
+        <v>3050.987797715586</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>XS007-A</t>
+          <t>XS007-B</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -4384,10 +4384,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>1960</v>
+        <v>1985</v>
       </c>
       <c r="B202" t="n">
-        <v>312.6101402575088</v>
+        <v>3229.805223085192</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -4407,14 +4407,14 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>1960</v>
+        <v>1986</v>
       </c>
       <c r="B203" t="n">
-        <v>283.8765450201491</v>
+        <v>3381.698867777098</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>XS007-C</t>
+          <t>XS007-B</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -4430,14 +4430,14 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>1961</v>
+        <v>1987</v>
       </c>
       <c r="B204" t="n">
-        <v>310.266</v>
+        <v>3562.367751735816</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>XS007-A</t>
+          <t>XS007-B</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -4453,10 +4453,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>1961</v>
+        <v>1988</v>
       </c>
       <c r="B205" t="n">
-        <v>321.9175464872374</v>
+        <v>3794.134502412667</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -4476,14 +4476,14 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>1961</v>
+        <v>1989</v>
       </c>
       <c r="B206" t="n">
-        <v>301.2765450201491</v>
+        <v>4026.067628090656</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>XS007-C</t>
+          <t>XS007-B</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -4499,14 +4499,14 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>1962</v>
+        <v>1990</v>
       </c>
       <c r="B207" t="n">
-        <v>333.9924528133036</v>
+        <v>4267.452171662989</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>XS007-A</t>
+          <t>XS007-B</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -4522,10 +4522,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>1962</v>
+        <v>1991</v>
       </c>
       <c r="B208" t="n">
-        <v>334.3294258339792</v>
+        <v>4378.866396135557</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -4545,14 +4545,14 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>1962</v>
+        <v>1992</v>
       </c>
       <c r="B209" t="n">
-        <v>321.0765450201491</v>
+        <v>4537.040182182915</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>XS007-C</t>
+          <t>XS007-B</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -4568,14 +4568,14 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>1963</v>
+        <v>1993</v>
       </c>
       <c r="B210" t="n">
-        <v>342.026</v>
+        <v>4762.924985922399</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>XS007-A</t>
+          <t>XS007-B</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -4591,10 +4591,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>1963</v>
+        <v>1994</v>
       </c>
       <c r="B211" t="n">
-        <v>347.3337766832103</v>
+        <v>5041.663839183284</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -4614,14 +4614,14 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>1963</v>
+        <v>1995</v>
       </c>
       <c r="B212" t="n">
-        <v>341.8765450201491</v>
+        <v>5354.380678958654</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>XS007-C</t>
+          <t>XS007-B</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -4637,14 +4637,14 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>1964</v>
+        <v>1996</v>
       </c>
       <c r="B213" t="n">
-        <v>365.551</v>
+        <v>5659.998161322698</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>XS007-A</t>
+          <t>XS007-B</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -4660,10 +4660,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>1964</v>
+        <v>1997</v>
       </c>
       <c r="B214" t="n">
-        <v>369.7811391065325</v>
+        <v>6012.776520802989</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -4683,14 +4683,14 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>1964</v>
+        <v>1998</v>
       </c>
       <c r="B215" t="n">
-        <v>367.1765450201492</v>
+        <v>6394.779633517761</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>XS007-C</t>
+          <t>XS007-B</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -4706,14 +4706,14 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>1965</v>
+        <v>1999</v>
       </c>
       <c r="B216" t="n">
-        <v>395.297</v>
+        <v>6822.509021583856</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>XS007-A</t>
+          <t>XS007-B</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -4729,10 +4729,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>1965</v>
+        <v>2000</v>
       </c>
       <c r="B217" t="n">
-        <v>400.009371190676</v>
+        <v>7360.045670242368</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -4752,14 +4752,14 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>1965</v>
+        <v>2001</v>
       </c>
       <c r="B218" t="n">
-        <v>400.0765450201492</v>
+        <v>7791.451621760327</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>XS007-C</t>
+          <t>XS007-B</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -4775,14 +4775,14 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>1966</v>
+        <v>2002</v>
       </c>
       <c r="B219" t="n">
-        <v>432.034</v>
+        <v>8081.207155757907</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>XS007-A</t>
+          <t>XS007-B</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -4798,10 +4798,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>1966</v>
+        <v>2003</v>
       </c>
       <c r="B220" t="n">
-        <v>441.0617068986242</v>
+        <v>8329.410323754952</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -4821,14 +4821,14 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>1966</v>
+        <v>2004</v>
       </c>
       <c r="B221" t="n">
-        <v>440.0765450201492</v>
+        <v>8959.628925720437</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>XS007-C</t>
+          <t>XS007-B</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -4844,14 +4844,14 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>1967</v>
+        <v>2005</v>
       </c>
       <c r="B222" t="n">
-        <v>467.446</v>
+        <v>9709.594044177349</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>XS007-A</t>
+          <t>XS007-B</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -4867,10 +4867,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>1967</v>
+        <v>2006</v>
       </c>
       <c r="B223" t="n">
-        <v>482.69379367734</v>
+        <v>10479.59960073247</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -4890,14 +4890,14 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>1967</v>
+        <v>2007</v>
       </c>
       <c r="B224" t="n">
-        <v>478.9765450201492</v>
+        <v>11016.56182755367</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>XS007-C</t>
+          <t>XS007-B</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -4913,14 +4913,14 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>1968</v>
+        <v>2008</v>
       </c>
       <c r="B225" t="n">
-        <v>504.865</v>
+        <v>11695.53919696291</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>XS007-A</t>
+          <t>XS007-B</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -4936,10 +4936,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>1968</v>
+        <v>2009</v>
       </c>
       <c r="B226" t="n">
-        <v>535.7669998366205</v>
+        <v>11239.33454381504</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -4959,14 +4959,14 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>1968</v>
+        <v>2010</v>
       </c>
       <c r="B227" t="n">
-        <v>521.2765450201491</v>
+        <v>11407.68674967562</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>XS007-C</t>
+          <t>XS007-B</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -4982,14 +4982,14 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>1969</v>
+        <v>2011</v>
       </c>
       <c r="B228" t="n">
-        <v>561.306</v>
+        <v>11798.68515343924</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>XS007-A</t>
+          <t>XS007-B</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -5005,14 +5005,14 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>1969</v>
+        <v>1925</v>
       </c>
       <c r="B229" t="n">
-        <v>595.4111587393223</v>
+        <v>69.2</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>XS007-B</t>
+          <t>XS007-C</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -5028,10 +5028,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>1969</v>
+        <v>1926</v>
       </c>
       <c r="B230" t="n">
-        <v>568.9765450201492</v>
+        <v>72.30000000000001</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -5051,14 +5051,14 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>1970</v>
+        <v>1927</v>
       </c>
       <c r="B231" t="n">
-        <v>599.465</v>
+        <v>77.80240045937882</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>XS007-A</t>
+          <t>XS007-C</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -5074,14 +5074,14 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>1970</v>
+        <v>1928</v>
       </c>
       <c r="B232" t="n">
-        <v>660.0082194553752</v>
+        <v>81.49883924817735</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>XS007-B</t>
+          <t>XS007-C</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -5097,10 +5097,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>1970</v>
+        <v>1929</v>
       </c>
       <c r="B233" t="n">
-        <v>615.9765450201492</v>
+        <v>86.32882294433108</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -5120,14 +5120,14 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>1971</v>
+        <v>1930</v>
       </c>
       <c r="B234" t="n">
-        <v>728.0561900232797</v>
+        <v>89.70054448694155</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>XS007-B</t>
+          <t>XS007-C</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -5143,10 +5143,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>1971</v>
+        <v>1931</v>
       </c>
       <c r="B235" t="n">
-        <v>662.8765450201491</v>
+        <v>84.74008080145197</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -5166,14 +5166,14 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>1972</v>
+        <v>1932</v>
       </c>
       <c r="B236" t="n">
-        <v>795.5806463073883</v>
+        <v>80.47724024076372</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>XS007-B</t>
+          <t>XS007-C</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -5189,10 +5189,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>1972</v>
+        <v>1933</v>
       </c>
       <c r="B237" t="n">
-        <v>717.9765450201492</v>
+        <v>77.81203818586386</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
@@ -5212,14 +5212,14 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>1973</v>
+        <v>1934</v>
       </c>
       <c r="B238" t="n">
-        <v>905.1470932422044</v>
+        <v>76.17584877413533</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>XS007-B</t>
+          <t>XS007-C</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -5235,10 +5235,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>1973</v>
+        <v>1935</v>
       </c>
       <c r="B239" t="n">
-        <v>788.4765450201492</v>
+        <v>74.49221209355741</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -5258,14 +5258,14 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>1974</v>
+        <v>1936</v>
       </c>
       <c r="B240" t="n">
-        <v>1112.967142133053</v>
+        <v>72.55947725152015</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>XS007-B</t>
+          <t>XS007-C</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -5281,10 +5281,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>1974</v>
+        <v>1937</v>
       </c>
       <c r="B241" t="n">
-        <v>871.3765450201491</v>
+        <v>74.37359392143392</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -5304,14 +5304,14 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>1975</v>
+        <v>1938</v>
       </c>
       <c r="B242" t="n">
-        <v>1239.942598214263</v>
+        <v>73.61666171057084</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>XS007-B</t>
+          <t>XS007-C</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -5327,10 +5327,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>1975</v>
+        <v>1939</v>
       </c>
       <c r="B243" t="n">
-        <v>951.5765450201492</v>
+        <v>74.30390574531137</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
@@ -5350,14 +5350,14 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>1976</v>
+        <v>1940</v>
       </c>
       <c r="B244" t="n">
-        <v>1365.520802998242</v>
+        <v>74.2950093824021</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>XS007-B</t>
+          <t>XS007-C</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -5373,10 +5373,10 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>1976</v>
+        <v>1941</v>
       </c>
       <c r="B245" t="n">
-        <v>1040.476545020149</v>
+        <v>74.65382935307568</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -5396,14 +5396,14 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>1977</v>
+        <v>1942</v>
       </c>
       <c r="B246" t="n">
-        <v>1524.571604949191</v>
+        <v>73.96732668191093</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>XS007-B</t>
+          <t>XS007-C</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -5419,10 +5419,10 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>1977</v>
+        <v>1943</v>
       </c>
       <c r="B247" t="n">
-        <v>1152.176545020149</v>
+        <v>72.45197953303324</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
@@ -5442,14 +5442,14 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>1978</v>
+        <v>1944</v>
       </c>
       <c r="B248" t="n">
-        <v>1739.358507204221</v>
+        <v>70.52443423602637</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>XS007-B</t>
+          <t>XS007-C</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -5465,10 +5465,10 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>1978</v>
+        <v>1945</v>
       </c>
       <c r="B249" t="n">
-        <v>1297.976545020149</v>
+        <v>68.24770669483097</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
@@ -5488,14 +5488,14 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>1979</v>
+        <v>1946</v>
       </c>
       <c r="B250" t="n">
-        <v>2010.474141529709</v>
+        <v>74.38026619361587</v>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>XS007-B</t>
+          <t>XS007-C</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -5511,10 +5511,10 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>1979</v>
+        <v>1947</v>
       </c>
       <c r="B251" t="n">
-        <v>1476.276545020149</v>
+        <v>83.17654502014911</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>
@@ -5534,14 +5534,14 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>1980</v>
+        <v>1948</v>
       </c>
       <c r="B252" t="n">
-        <v>2318.022960056148</v>
+        <v>95.77654502014911</v>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>XS007-B</t>
+          <t>XS007-C</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -5557,10 +5557,10 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>1980</v>
+        <v>1949</v>
       </c>
       <c r="B253" t="n">
-        <v>1668.576545020149</v>
+        <v>105.9765450201491</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
@@ -5580,14 +5580,14 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>1981</v>
+        <v>1950</v>
       </c>
       <c r="B254" t="n">
-        <v>2626.419874620664</v>
+        <v>116.8765450201491</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>XS007-B</t>
+          <t>XS007-C</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -5603,10 +5603,10 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>1981</v>
+        <v>1951</v>
       </c>
       <c r="B255" t="n">
-        <v>1887.176545020149</v>
+        <v>130.8765450201491</v>
       </c>
       <c r="C255" t="inlineStr">
         <is>
@@ -5626,14 +5626,14 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>1982</v>
+        <v>1952</v>
       </c>
       <c r="B256" t="n">
-        <v>2790.590639341792</v>
+        <v>145.0765450201491</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>XS007-B</t>
+          <t>XS007-C</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -5649,10 +5649,10 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>1982</v>
+        <v>1953</v>
       </c>
       <c r="B257" t="n">
-        <v>2093.776545020149</v>
+        <v>160.5765450201491</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
@@ -5672,14 +5672,14 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>1983</v>
+        <v>1954</v>
       </c>
       <c r="B258" t="n">
-        <v>2873.790280472474</v>
+        <v>174.5765450201491</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>XS007-B</t>
+          <t>XS007-C</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -5695,10 +5695,10 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>1983</v>
+        <v>1955</v>
       </c>
       <c r="B259" t="n">
-        <v>2280.876545020149</v>
+        <v>190.0765450201491</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
@@ -5718,14 +5718,14 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>1984</v>
+        <v>1956</v>
       </c>
       <c r="B260" t="n">
-        <v>3050.987797715586</v>
+        <v>210.1765450201491</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>XS007-B</t>
+          <t>XS007-C</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -5741,10 +5741,10 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>1984</v>
+        <v>1957</v>
       </c>
       <c r="B261" t="n">
-        <v>2509.676545020149</v>
+        <v>232.0765450201491</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
@@ -5764,14 +5764,14 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>1985</v>
+        <v>1958</v>
       </c>
       <c r="B262" t="n">
-        <v>3229.805223085192</v>
+        <v>248.0765450201491</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>XS007-B</t>
+          <t>XS007-C</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -5787,10 +5787,10 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>1985</v>
+        <v>1959</v>
       </c>
       <c r="B263" t="n">
-        <v>2751.176545020149</v>
+        <v>265.2765450201491</v>
       </c>
       <c r="C263" t="inlineStr">
         <is>
@@ -5810,14 +5810,14 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>1986</v>
+        <v>1960</v>
       </c>
       <c r="B264" t="n">
-        <v>3381.698867777098</v>
+        <v>283.8765450201491</v>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>XS007-B</t>
+          <t>XS007-C</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -5833,10 +5833,10 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>1986</v>
+        <v>1961</v>
       </c>
       <c r="B265" t="n">
-        <v>2964.576545020149</v>
+        <v>301.2765450201491</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
@@ -5856,14 +5856,14 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>1987</v>
+        <v>1962</v>
       </c>
       <c r="B266" t="n">
-        <v>3562.367751735816</v>
+        <v>321.0765450201491</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>XS007-B</t>
+          <t>XS007-C</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -5879,10 +5879,10 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>1987</v>
+        <v>1963</v>
       </c>
       <c r="B267" t="n">
-        <v>3157.276545020149</v>
+        <v>341.8765450201491</v>
       </c>
       <c r="C267" t="inlineStr">
         <is>
@@ -5902,14 +5902,14 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>1988</v>
+        <v>1964</v>
       </c>
       <c r="B268" t="n">
-        <v>3794.134502412666</v>
+        <v>367.1765450201491</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>XS007-B</t>
+          <t>XS007-C</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -5925,10 +5925,10 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>1988</v>
+        <v>1965</v>
       </c>
       <c r="B269" t="n">
-        <v>3361.076545020149</v>
+        <v>400.0765450201492</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
@@ -5948,14 +5948,14 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>1989</v>
+        <v>1966</v>
       </c>
       <c r="B270" t="n">
-        <v>4026.067628090656</v>
+        <v>440.0765450201492</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>XS007-B</t>
+          <t>XS007-C</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -5971,10 +5971,10 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>1989</v>
+        <v>1967</v>
       </c>
       <c r="B271" t="n">
-        <v>3585.276545020149</v>
+        <v>478.9765450201492</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
@@ -5994,14 +5994,14 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>1990</v>
+        <v>1968</v>
       </c>
       <c r="B272" t="n">
-        <v>4267.452171662989</v>
+        <v>521.2765450201491</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>XS007-B</t>
+          <t>XS007-C</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -6017,10 +6017,10 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>1990</v>
+        <v>1969</v>
       </c>
       <c r="B273" t="n">
-        <v>3822.876545020149</v>
+        <v>568.9765450201492</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
@@ -6040,14 +6040,14 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>1991</v>
+        <v>1970</v>
       </c>
       <c r="B274" t="n">
-        <v>4378.866396135557</v>
+        <v>615.9765450201492</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>XS007-B</t>
+          <t>XS007-C</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -6063,10 +6063,10 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>1991</v>
+        <v>1971</v>
       </c>
       <c r="B275" t="n">
-        <v>4021.976545020149</v>
+        <v>662.8765450201491</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
@@ -6086,14 +6086,14 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>1992</v>
+        <v>1972</v>
       </c>
       <c r="B276" t="n">
-        <v>4537.040182182915</v>
+        <v>717.9765450201492</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>XS007-B</t>
+          <t>XS007-C</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -6109,10 +6109,10 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>1992</v>
+        <v>1973</v>
       </c>
       <c r="B277" t="n">
-        <v>4214.676545020149</v>
+        <v>788.4765450201492</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
@@ -6132,14 +6132,14 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>1993</v>
+        <v>1974</v>
       </c>
       <c r="B278" t="n">
-        <v>4762.924985922399</v>
+        <v>871.3765450201491</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>XS007-B</t>
+          <t>XS007-C</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -6155,10 +6155,10 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>1993</v>
+        <v>1975</v>
       </c>
       <c r="B279" t="n">
-        <v>4440.576545020149</v>
+        <v>951.5765450201492</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
@@ -6178,14 +6178,14 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>1994</v>
+        <v>1976</v>
       </c>
       <c r="B280" t="n">
-        <v>5041.663839183284</v>
+        <v>1040.476545020149</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>XS007-B</t>
+          <t>XS007-C</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -6201,10 +6201,10 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>1994</v>
+        <v>1977</v>
       </c>
       <c r="B281" t="n">
-        <v>4706.476545020148</v>
+        <v>1152.176545020149</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
@@ -6224,14 +6224,14 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>1995</v>
+        <v>1978</v>
       </c>
       <c r="B282" t="n">
-        <v>5354.380678958654</v>
+        <v>1297.976545020149</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>XS007-B</t>
+          <t>XS007-C</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -6247,10 +6247,10 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>1995</v>
+        <v>1979</v>
       </c>
       <c r="B283" t="n">
-        <v>5027.076545020149</v>
+        <v>1476.276545020149</v>
       </c>
       <c r="C283" t="inlineStr">
         <is>
@@ -6270,14 +6270,14 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>1996</v>
+        <v>1980</v>
       </c>
       <c r="B284" t="n">
-        <v>5659.998161322698</v>
+        <v>1668.576545020149</v>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>XS007-B</t>
+          <t>XS007-C</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -6293,10 +6293,10 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>1996</v>
+        <v>1981</v>
       </c>
       <c r="B285" t="n">
-        <v>5383.176545020149</v>
+        <v>1887.176545020149</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
@@ -6316,14 +6316,14 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>1997</v>
+        <v>1982</v>
       </c>
       <c r="B286" t="n">
-        <v>6012.776520802989</v>
+        <v>2093.776545020149</v>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>XS007-B</t>
+          <t>XS007-C</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -6339,10 +6339,10 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>1997</v>
+        <v>1983</v>
       </c>
       <c r="B287" t="n">
-        <v>5774.376545020149</v>
+        <v>2280.876545020149</v>
       </c>
       <c r="C287" t="inlineStr">
         <is>
@@ -6362,14 +6362,14 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>1998</v>
+        <v>1984</v>
       </c>
       <c r="B288" t="n">
-        <v>6394.779633517761</v>
+        <v>2509.676545020149</v>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>XS007-B</t>
+          <t>XS007-C</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -6385,10 +6385,10 @@
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>1998</v>
+        <v>1985</v>
       </c>
       <c r="B289" t="n">
-        <v>6202.376545020149</v>
+        <v>2751.176545020149</v>
       </c>
       <c r="C289" t="inlineStr">
         <is>
@@ -6408,14 +6408,14 @@
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>1999</v>
+        <v>1986</v>
       </c>
       <c r="B290" t="n">
-        <v>6822.509021583856</v>
+        <v>2964.576545020149</v>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>XS007-B</t>
+          <t>XS007-C</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -6431,10 +6431,10 @@
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>1999</v>
+        <v>1987</v>
       </c>
       <c r="B291" t="n">
-        <v>6666.276545020149</v>
+        <v>3157.276545020149</v>
       </c>
       <c r="C291" t="inlineStr">
         <is>
@@ -6454,14 +6454,14 @@
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>2000</v>
+        <v>1988</v>
       </c>
       <c r="B292" t="n">
-        <v>7360.045670242368</v>
+        <v>3361.076545020149</v>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>XS007-B</t>
+          <t>XS007-C</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -6477,10 +6477,10 @@
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>2000</v>
+        <v>1989</v>
       </c>
       <c r="B293" t="n">
-        <v>7177.376545020148</v>
+        <v>3585.276545020149</v>
       </c>
       <c r="C293" t="inlineStr">
         <is>
@@ -6500,14 +6500,14 @@
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>2001</v>
+        <v>1990</v>
       </c>
       <c r="B294" t="n">
-        <v>7791.451621760327</v>
+        <v>3822.876545020149</v>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>XS007-B</t>
+          <t>XS007-C</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -6523,10 +6523,10 @@
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>2001</v>
+        <v>1991</v>
       </c>
       <c r="B295" t="n">
-        <v>7593.776545020148</v>
+        <v>4021.976545020149</v>
       </c>
       <c r="C295" t="inlineStr">
         <is>
@@ -6546,14 +6546,14 @@
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>2002</v>
+        <v>1992</v>
       </c>
       <c r="B296" t="n">
-        <v>8081.207155757907</v>
+        <v>4214.676545020149</v>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>XS007-B</t>
+          <t>XS007-C</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -6569,10 +6569,10 @@
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>2002</v>
+        <v>1993</v>
       </c>
       <c r="B297" t="n">
-        <v>7851.476545020148</v>
+        <v>4440.576545020149</v>
       </c>
       <c r="C297" t="inlineStr">
         <is>
@@ -6592,14 +6592,14 @@
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>2003</v>
+        <v>1994</v>
       </c>
       <c r="B298" t="n">
-        <v>8329.410323754952</v>
+        <v>4706.476545020148</v>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>XS007-B</t>
+          <t>XS007-C</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -6615,10 +6615,10 @@
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>2003</v>
+        <v>1995</v>
       </c>
       <c r="B299" t="n">
-        <v>8074.576545020147</v>
+        <v>5027.076545020149</v>
       </c>
       <c r="C299" t="inlineStr">
         <is>
@@ -6638,14 +6638,14 @@
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>2004</v>
+        <v>1996</v>
       </c>
       <c r="B300" t="n">
-        <v>8959.628925720437</v>
+        <v>5383.176545020149</v>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>XS007-B</t>
+          <t>XS007-C</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -6661,10 +6661,10 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>2004</v>
+        <v>1997</v>
       </c>
       <c r="B301" t="n">
-        <v>8342.776545020148</v>
+        <v>5774.376545020149</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
@@ -6684,14 +6684,14 @@
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>2005</v>
+        <v>1998</v>
       </c>
       <c r="B302" t="n">
-        <v>9709.594044177349</v>
+        <v>6202.376545020149</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>XS007-B</t>
+          <t>XS007-C</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -6707,10 +6707,10 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>2005</v>
+        <v>1999</v>
       </c>
       <c r="B303" t="n">
-        <v>8700.876545020148</v>
+        <v>6666.276545020149</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
@@ -6730,14 +6730,14 @@
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>2006</v>
+        <v>2000</v>
       </c>
       <c r="B304" t="n">
-        <v>10479.59960073247</v>
+        <v>7177.376545020148</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>XS007-B</t>
+          <t>XS007-C</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -6753,10 +6753,10 @@
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>2006</v>
+        <v>2001</v>
       </c>
       <c r="B305" t="n">
-        <v>9165.976545020148</v>
+        <v>7593.776545020148</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
@@ -6776,14 +6776,14 @@
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>2007</v>
+        <v>2002</v>
       </c>
       <c r="B306" t="n">
-        <v>11016.56182755366</v>
+        <v>7851.476545020148</v>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>XS007-B</t>
+          <t>XS007-C</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -6799,10 +6799,10 @@
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>2007</v>
+        <v>2003</v>
       </c>
       <c r="B307" t="n">
-        <v>9706.876545020148</v>
+        <v>8074.576545020147</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
@@ -6822,14 +6822,14 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>2008</v>
+        <v>2004</v>
       </c>
       <c r="B308" t="n">
-        <v>11695.53919696292</v>
+        <v>8342.776545020148</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>XS007-B</t>
+          <t>XS007-C</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -6845,10 +6845,10 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>2008</v>
+        <v>2005</v>
       </c>
       <c r="B309" t="n">
-        <v>10229.67654502015</v>
+        <v>8700.876545020148</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
@@ -6868,14 +6868,14 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>2009</v>
+        <v>2006</v>
       </c>
       <c r="B310" t="n">
-        <v>11239.33454381504</v>
+        <v>9165.976545020148</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>XS007-B</t>
+          <t>XS007-C</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -6891,10 +6891,10 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>2009</v>
+        <v>2007</v>
       </c>
       <c r="B311" t="n">
-        <v>10447.57654502015</v>
+        <v>9706.876545020148</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
@@ -6914,14 +6914,14 @@
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="B312" t="n">
-        <v>11407.68674967562</v>
+        <v>10229.67654502015</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>XS007-B</t>
+          <t>XS007-C</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -6937,10 +6937,10 @@
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="B313" t="n">
-        <v>10643.17654502015</v>
+        <v>10447.57654502015</v>
       </c>
       <c r="C313" t="inlineStr">
         <is>
@@ -6960,14 +6960,14 @@
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="B314" t="n">
-        <v>11798.68515343924</v>
+        <v>10643.17654502015</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>XS007-B</t>
+          <t>XS007-C</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -7072,7 +7072,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GPIM Variant - IRS Adjusted</t>
+          <t>Generalized Perpetual Inventory Method (GPIM) variant, IRS-adjusted.</t>
         </is>
       </c>
     </row>
@@ -7092,7 +7092,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Source: Appendix Table 6.8.II.4 (Great Depression / WWII correction). UNIT NORMALIZATION: raw IRS Series V 115 (KTHcorpirs) is in thousands of dollars and divided by 1000 at load time to convert to billions. XS007 has no extension (historical 1925-1947 correction only). See `CH6_GPIM_SUMMARY.md` for the full Ch6 construction pipeline.</t>
+          <t>Source: Shaikh (2016), Appendix Table 6.8.II.4 (Great Depression / WWII correction). Unit normalization: the raw IRS Series V 115 values (`KTHcorpirs`) are in thousands of dollars and are divided by 1000 at load time to convert to billions. XS007 has no extension (historical 1925-1947 correction only).</t>
         </is>
       </c>
     </row>
@@ -7150,7 +7150,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>The canonical Shaikh-published values are transcribed from `SalvagedInputs/book_data/ShaikhChoppedTables/Appendix6_Table68*.xlsx` (Appendix 6.8). Upstream agencies are BEA (NIPA / Fixed Asset Accounts), IRS SOI, U.S. Census Bureau Historical Statistics 1975 (IRS book values), and FRB G.17. All public domain.</t>
+          <t>The `-A`, `-B`, and `-C` suffixes label the individual sub-variants of this series. The canonical Shaikh-published values are transcribed from the published Chapter 6 appendix workbook (Shaikh 2016, Appendix 6.8). Upstream agencies are the Bureau of Economic Analysis (BEA) — its National Income and Product Accounts (NIPA) and Fixed Asset accounts (FA) — the IRS Statistics of Income (SOI), the U.S. Census Bureau Historical Statistics 1975 (IRS book values), and the Federal Reserve Board G.17 release. All public domain.</t>
         </is>
       </c>
     </row>
@@ -7190,7 +7190,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Book period: 1925-2011. Vintage-stable extension recipe in `XS007_EPR.md`.</t>
+          <t>Book period: 1925-2011. See the companion Extension Provenance Record for the vintage-stable extension recipe.</t>
         </is>
       </c>
     </row>
@@ -7270,7 +7270,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>`V03_XS007_validate.py` round-trip-validates against the Appendix 6.8 source workbook at 1.5% tolerance. Per the Phase 4 adequacy report (`CH6_ADEQUACY_REPORT.json`), Phase 5 blockers B2 (NIPA T7.11 FISIM remap, resolver in `_nipa_t711_line_resolver.py`) and B3 (BEA 1993 depreciation rates, staged at `Reconstructed/BEA_1993_FA_methodology/`) are RESOLVED.</t>
+          <t>The series round-trip-validates against the Appendix 6.8 source workbook at 1.5% tolerance. Two construction dependencies are resolved: the remapping of the NIPA Table 7.11 financial services indirectly measured (FISIM) lines, and the BEA 1993 depreciation rates.</t>
         </is>
       </c>
     </row>
@@ -7313,7 +7313,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Per the Ch6 GPIM construction pipeline (see `Technical/docs/chapters/CH6_GPIM_SUMMARY.md`) and the Anu Framework anti-degradation rule, **extension does NOT splice the published XS007 values**. Instead, the extension re-fetches the underlying NIPA / BEA Fixed Asset / IRS / Census components and re-runs the formula end-to-end at the current vintage.</t>
+          <t>Following the Chapter 6 Generalized Perpetual Inventory Method (GPIM) construction pipeline and the project's anti-degradation rule, **extension does NOT splice the published XS007 values**. Instead, the extension re-fetches the underlying National Income and Product Accounts (NIPA), BEA Fixed Asset, IRS, and Census components and re-runs the formula end-to-end at the current vintage.</t>
         </is>
       </c>
     </row>
@@ -7343,7 +7343,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>For XS007, the Phase 5 round-trip validation reads `XS007_raw.parquet` from the Appendix 6.8 workbook and confirms bit-for-bit reproduction of the published series for the book period 1925-2011. A worked-example year (typically 2009 per book p. 842, or 2011 per Shaikh's last published vintage) verifies headline values.</t>
+          <t>For XS007, the round-trip validation reads the raw values from the Appendix 6.8 workbook and confirms bit-for-bit reproduction of the published series for the book period 1925-2011. A worked-example year (typically 2009 per book p. 842, or 2011 per Shaikh's last published vintage) verifies headline values.</t>
         </is>
       </c>
     </row>
@@ -7353,7 +7353,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>## No-Proxy Disclosure</t>
+          <t>## Proxy Use</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>No proxies are used in the book period. Book period is fully sourced from primary BEA / IRS / Census; no proxies.</t>
+          <t>No proxies are used in the book period; it is fully sourced from primary BEA / IRS / Census data.</t>
         </is>
       </c>
     </row>
@@ -7373,7 +7373,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>## No-Synthetic Disclosure</t>
+          <t>## Synthetic Values</t>
         </is>
       </c>
     </row>
@@ -7383,7 +7383,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>No synthetic values, interpolations, or freezes are used. All values are verbatim from Shaikh's posted Appendix 6.8 chopped tables (MD5-verified per `SalvagedInputs/book_data/Reconstructed/BEA_1993_FA_methodology/README.md` for the BEA 1993 staged inputs).</t>
+          <t>No synthetic values, interpolations, or freezes are used. All values are verbatim from Shaikh's posted Appendix 6.8 chopped tables (MD5-verified against the reconstructed BEA 1993 staged inputs).</t>
         </is>
       </c>
     </row>
@@ -7417,35 +7417,35 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>| Appendix workbook missing or corrupted | `_ch6_appendix_loader` raises `FileNotFoundError` or empty DataFrame | L01 returns `status: FAIL` with explicit path |</t>
+          <t>| Appendix workbook missing or corrupted | The appendix loader raises a file-not-found error or returns an empty table | Loading fails with an explicit error |</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>| Variable name not in workbook | `load_variables` returns empty DataFrame | L01 records 0 rows for that subseries; V03 flags as missing |</t>
+          <t>| Variable name not in workbook | The variable lookup returns no rows | Zero rows are recorded for that subseries and validation flags it as missing |</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>| BEA / IRS vintage drift during extension | EPR-documented re-fetch script logs vintage_year; V03 tolerance widens for extension rows | Documented per-year; no silent overwrite of book period |</t>
+          <t>| BEA / IRS vintage drift during extension | The re-fetch logs the vintage year; validation tolerance widens for extension rows | Documented per-year; no silent overwrite of the book period |</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>| FISIM T7.11 line revision (XS003) | `_nipa_t711_line_resolver` falls back to nearest pinned vintage with logged warning | Re-mapped by stub label; vintage logged in resolver output |</t>
+          <t>| NIPA Table 7.11 financial services indirectly measured (FISIM) line revision (affecting XS003) | The line resolver falls back to the nearest pinned vintage with a logged warning | Re-mapped by label; vintage logged |</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>| BEA 1993 depreciation rate not available post-2011 | XS004/XS006/XS007 freeze depreciation rate inputs at 2011-vintage projection | Documented in `BEA_1993_FA_methodology/README.md` |</t>
+          <t>| BEA 1993 depreciation rate not available post-2011 | XS004/XS006/XS007 freeze depreciation-rate inputs at 2011-vintage projection | Documented with the reconstructed BEA 1993 Fixed Asset methodology inputs |</t>
         </is>
       </c>
     </row>
@@ -7455,7 +7455,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>## CD2 Divergence Pre-Disclosure</t>
+          <t>## Divergence From an Earlier Replication</t>
         </is>
       </c>
     </row>
@@ -7465,7 +7465,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>CD2 S212 raw values are ~1000x larger than expected (thousands vs billions). Loader normalizes via scale = 1/1000.</t>
+          <t>In an earlier replication the raw values were ~1000× larger than expected (thousands vs billions). The loader normalizes them via scale = 1/1000.</t>
         </is>
       </c>
     </row>
@@ -7475,7 +7475,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>## Anti-Degradation Compliance</t>
+          <t>## Extension Integrity</t>
         </is>
       </c>
     </row>
@@ -7485,7 +7485,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Per Anu Framework: extension MUST re-fetch the BEA / IRS / FRB component series and re-compute the formula end-to-end. Splicing the published series is FORBIDDEN. Loader caches BEA / FRED responses per `S00_cache` with 30-day TTL (book-period values: TTL=None).</t>
+          <t>Extension must re-fetch the BEA / IRS / FRB component series and re-compute the formula end-to-end; splicing the published series is not permitted. Fetched BEA / FRED responses are cached with a 30-day time-to-live (book-period values are cached permanently).</t>
         </is>
       </c>
     </row>
@@ -7844,7 +7844,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-05-18T22:50:10.595806+00:00</t>
+          <t>2026-07-02T06:27:45.694394+00:00</t>
         </is>
       </c>
     </row>

--- a/extenbooks/XS007_extenbook.xlsx
+++ b/extenbooks/XS007_extenbook.xlsx
@@ -7844,7 +7844,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-02T06:27:45.694394+00:00</t>
+          <t>2026-07-11T03:44:27.583124+00:00</t>
         </is>
       </c>
     </row>
@@ -7859,11 +7859,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7886,6 +7886,162 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>primary_source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SHAIKH_APPENDIX_6_8</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>book_period_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>validation_class</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pipeline_consistent</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>triage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{"verdict": "publish", "reason": "Methodology variant of XS004 applying the IRS book-value index to correct the corporate capital stock through the Great Depression / WWII window (1925-1947), since the BEA measure assumes scrapping is independent of economic conditions. All billions_current_usd after the documented IRS thousands-to-billions normalization; single-unit, renders sensibly. Appendix Table 6.8.II.4.", "date": "2026-06-10"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dpr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/XS007_DPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>epr</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/XS007_EPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Source: Appendix Table 6.8.II.4 (Great Depression / WWII correction). UNIT NORMALIZATION: raw IRS Series V 115 (KTHcorpirs) is in thousands of dollars and divided by 1000 at load time to convert to billions. XS007 has no extension (historical 1925-1947 correction only).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>billions_current_usd</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
